--- a/pacjenci/MATYLDA FIREK.xlsx
+++ b/pacjenci/MATYLDA FIREK.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">

--- a/pacjenci/MATYLDA FIREK.xlsx
+++ b/pacjenci/MATYLDA FIREK.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>29.03.2021</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 78 mg%.</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Bardzo liczne, aktywne metabolicznie, spakietowane węzły chłonne szyjne po stronie prawej grup: 2B,3,4, 5A, 5B wielkości do 51x26 mm wg PET [Im fuz. 82] na długości do 68 mm wg PET SUV max do 16,5. Bardzo liczne, aktywne metabolicznie, spakietowane węzły chłonne szyjne po stronie lewej grup:2B,3,4, 5A, 5B  wielkości do 76x41 mm wg PET [Im fuz. 84 ] na długości do 106 mm wg PET SUV max do 20,1. Aktywny metabolicznie naciek w topografii węzłów chłonnych grupy 6 obustronnie na obszarze wielkości ok. 34x35 mm wg PET SUV max do 14,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie, spakietowane węzły chłonne: - śródpiersiowe prawe na obszarze wielkości ok 56x64x76 mm wg PET SUV max do 15,5 [Im fuz. 106] oraz na obszarze wielkości 59x26x34 mm wg PET SUV max 16,6  [Im fuz. 118] - śródpiersiowe lewe na obszarze wielkości ok. 75x39x 54 mm wg PET SUV max do 14,0 [Im fuz. 112]. - okołoaortalne obustronnie na poziomie Th8 wielkości do 13 mm wg PET SUV max do 6,0 Aktywny metabolicznie naciek w topografii węzłów chłonnych podostrogowych oraz obu wnęk płuc na obszarze wielkości 113x50 mm wg PET SUV max 14,0 [Im fuz. 126]  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w worku osierdziowym o grubości płaszcza ok 11 mm. Płyn w lewej jamie opłucnowej o grubości płaszcza do 15 mm.  Brzuch i miednica: Aktywne metaboliczne obszary w śledzionie wielkości do 32x26x26 mm wg PET SUV max do 9,9. Aktywne metabolicznie węzły chłonne we wnęce śledziony wielkości 24x17 mm SUV max do 7,2. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Aktywny metabolicznie obszar w łuku żebra 6 lewego średnicy 7 mm wg PET SUV max 6,2 [Im fuz. 146] Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax 1,8 Prawy płat wątroby SUVmax do 2,3</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem śledziony, pojedynczego żebra oraz węzłów chłonnych po obu stronach przepony (masywne zajęcie węzłów chłonnych szyi i śródpiersia).</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>20.1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>17.05.2021</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena odpowiedzi po 2 cyklach ABVD.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 61min od podania 18F-FDG. Glikemia: 80mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej, SUV max do 24,0, w jej obrębie widoczne są drobne węzły chłonne. Spakietowane węzły chłonne grupy VI po stronie lewej wielkości do 30x14mm wg PET, SUV max do 3,8 [Im fuz 86]. Węzły chłonne grupy V po stronie lewej średnicy do 19mm, SUV max 3,0 Węzły chłonne grupy V po stronie prawej średnicy do 17mm, SUV max 4,0 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Masa resztkowa w śródpiersiu przednim po stronie lewej wielkości ok 23x64mm [Im fuz 112] oraz po stronie prawej 65x29mm [Im fuz 110] , w jej obrębie widoczne są obszary zwiększonego metabolizmu FDG średnicy wg PET do 14mm, SUV max do 6,4. Aktywne metabolicznie węzły chłonne śródpiersiowe, największe: - podostrogowe 44x19mm [SUV max 3,0 [I,m fuz 121] - przytchawicze górne prawe wielkości do 20x24mm [Im fuz 102] SUV max do 4,0, lewe 21x18mm SUV max 3,2 [Im fuz 105] Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej klatki piersiowej, SUV max do 21,0, w jej obrębie widoczne są drobne węzły chłonne. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieznacznie zwiększona ilość płynu w osierdziu.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masa miękkotkankowa we wnęce śledziony średnicy ok 22mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax  2,3 Prawy płat wątroby SUVmax do 2,7.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie obszarów w obrębie masy resztkowej w śródpiersiu przednim, węzłach przytchawiczych i podostrogowych oraz szyjnych po stronie lewej. W porównaniu do badania wyjściowego z 29.03.2021 znaczna regresja metaboliczna i radiologiczna zmian.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>24</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - wychwyt umiarkowanie większy od wątroby</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Częściowa odpowiedź metaboliczna na leczenie. Klasyfikacja Lugano: Partial Response (PR) - częściowa odpowiedź na leczenie. Deauville: 4 - wychwyt umiarkowanie większy od wątroby.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>16.09.2021</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak Hodgkina. Ocena po zakończeniu chemioterapii  (2 cykle ABVD + 4 cykle BEACOPP esk).</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 90mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>: Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej, SUV max do 7,4, w jej obrębie widoczne są pojedyncze bardzo drobne węzły chłonne. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne grupy IV po stronie lewej średnicy 20m [Im TK 244]. Węzły chłonne grupy V po stronie lewej średnicy do 11mm.  Klatka piersiowa i śródpiersie: Masa resztkowa w śródpiersiu przednim po stronie lewej wielkości ok 22x14mm [Im TK 286] oraz po stronie prawej średnicy 25x12mm [Im TK 304]. Węzły chłonne śródpiersiowe przytchawicze prawe średnicy do 9mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masa miękkotkankowa we wnęce śledziony średnicy ok 10mm [lm TK 443].  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.  Inne: Rozlana aktywność metaboliczna w mięśniach kończyny górnej prawej oraz obręczy barkowej po stronie prawej, mięśni lędźwiowych - w pierwszej kolejności zmiany przeciążeniowe. Aktywność metaboliczna w brunatnej tkance tłuszczowej karku, klatki piersiowej i jamy brzusznej.  Wartości referencyjne: MBPS SUVmax  2,0, Prawy płat wątroby SUVmax do 2,5.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej.  Masy resztkowe do kontroli.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>7.4</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/MATYLDA FIREK.xlsx
+++ b/pacjenci/MATYLDA FIREK.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 78 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Bardzo liczne, aktywne metabolicznie, spakietowane węzły chłonne szyjne po stronie prawej grup: 2B,3,4, 5A, 5B wielkości do 51x26 mm wg PET [Im fuz. 82] na długości do 68 mm wg PET SUV max do 16,5. Bardzo liczne, aktywne metabolicznie, spakietowane węzły chłonne szyjne po stronie lewej grup:2B,3,4, 5A, 5B  wielkości do 76x41 mm wg PET [Im fuz. 84 ] na długości do 106 mm wg PET SUV max do 20,1. Aktywny metabolicznie naciek w topografii węzłów chłonnych grupy 6 obustronnie na obszarze wielkości ok. 34x35 mm wg PET SUV max do 14,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Aktywne metabolicznie, spakietowane węzły chłonne: - śródpiersiowe prawe na obszarze wielkości ok 56x64x76 mm wg PET SUV max do 15,5 [Im fuz. 106] oraz na obszarze wielkości 59x26x34 mm wg PET SUV max 16,6  [Im fuz. 118] - śródpiersiowe lewe na obszarze wielkości ok. 75x39x 54 mm wg PET SUV max do 14,0 [Im fuz. 112]. - okołoaortalne obustronnie na poziomie Th8 wielkości do 13 mm wg PET SUV max do 6,0 Aktywny metabolicznie naciek w topografii węzłów chłonnych podostrogowych oraz obu wnęk płuc na obszarze wielkości 113x50 mm wg PET SUV max 14,0 [Im fuz. 126]  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w worku osierdziowym o grubości płaszcza ok 11 mm. Płyn w lewej jamie opłucnowej o grubości płaszcza do 15 mm.  Brzuch i miednica: Aktywne metaboliczne obszary w śledzionie wielkości do 32x26x26 mm wg PET SUV max do 9,9. Aktywne metabolicznie węzły chłonne we wnęce śledziony wielkości 24x17 mm SUV max do 7,2. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Aktywny metabolicznie obszar w łuku żebra 6 lewego średnicy 7 mm wg PET SUV max 6,2 [Im fuz. 146] Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax 1,8 Prawy płat wątroby SUVmax do 2,3</t>
+          <t>78</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Bardzo liczne, aktywne metabolicznie, spakietowane węzły chłonne szyjne po stronie prawej grup: 2B,3,4, 5A, 5B wielkości do 51x26 mm wg PET [Im fuz. 82] na długości do 68 mm wg PET SUV max do 16,5. Bardzo liczne, aktywne metabolicznie, spakietowane węzły chłonne szyjne po stronie lewej grup:2B,3,4, 5A, 5B  wielkości do 76x41 mm wg PET [Im fuz. 84 ] na długości do 106 mm wg PET SUV max do 20,1. Aktywny metabolicznie naciek w topografii węzłów chłonnych grupy 6 obustronnie na obszarze wielkości ok. 34x35 mm wg PET SUV max do 14,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Aktywne metabolicznie, spakietowane węzły chłonne: - śródpiersiowe prawe na obszarze wielkości ok 56x64x76 mm wg PET SUV max do 15,5 [Im fuz. 106] oraz na obszarze wielkości 59x26x34 mm wg PET SUV max 16,6  [Im fuz. 118] - śródpiersiowe lewe na obszarze wielkości ok. 75x39x 54 mm wg PET SUV max do 14,0 [Im fuz. 112]. - okołoaortalne obustronnie na poziomie Th8 wielkości do 13 mm wg PET SUV max do 6,0 Aktywny metabolicznie naciek w topografii węzłów chłonnych podostrogowych oraz obu wnęk płuc na obszarze wielkości 113x50 mm wg PET SUV max 14,0 [Im fuz. 126]  Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Płyn w worku osierdziowym o grubości płaszcza ok 11 mm. Płyn w lewej jamie opłucnowej o grubości płaszcza do 15 mm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Aktywne metaboliczne obszary w śledzionie wielkości do 32x26x26 mm wg PET SUV max do 9,9. Aktywne metabolicznie węzły chłonne we wnęce śledziony wielkości 24x17 mm SUV max do 7,2. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Aktywny metabolicznie obszar w łuku żebra 6 lewego średnicy 7 mm wg PET SUV max 6,2 [Im fuz. 146] Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnego metabolicznie procesu chłoniakowego z zajęciem śledziony, pojedynczego żebra oraz węzłów chłonnych po obu stronach przepony (masywne zajęcie węzłów chłonnych szyi i śródpiersia).</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>20.1</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 61min od podania 18F-FDG. Glikemia: 80mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej, SUV max do 24,0, w jej obrębie widoczne są drobne węzły chłonne. Spakietowane węzły chłonne grupy VI po stronie lewej wielkości do 30x14mm wg PET, SUV max do 3,8 [Im fuz 86]. Węzły chłonne grupy V po stronie lewej średnicy do 19mm, SUV max 3,0 Węzły chłonne grupy V po stronie prawej średnicy do 17mm, SUV max 4,0 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Masa resztkowa w śródpiersiu przednim po stronie lewej wielkości ok 23x64mm [Im fuz 112] oraz po stronie prawej 65x29mm [Im fuz 110] , w jej obrębie widoczne są obszary zwiększonego metabolizmu FDG średnicy wg PET do 14mm, SUV max do 6,4. Aktywne metabolicznie węzły chłonne śródpiersiowe, największe: - podostrogowe 44x19mm [SUV max 3,0 [I,m fuz 121] - przytchawicze górne prawe wielkości do 20x24mm [Im fuz 102] SUV max do 4,0, lewe 21x18mm SUV max 3,2 [Im fuz 105] Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej klatki piersiowej, SUV max do 21,0, w jej obrębie widoczne są drobne węzły chłonne. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieznacznie zwiększona ilość płynu w osierdziu.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masa miękkotkankowa we wnęce śledziony średnicy ok 22mm.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.  Wartości referencyjne: MBPS SUVmax  2,3 Prawy płat wątroby SUVmax do 2,7.</t>
+          <t>80</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej, SUV max do 24,0, w jej obrębie widoczne są drobne węzły chłonne. Spakietowane węzły chłonne grupy VI po stronie lewej wielkości do 30x14mm wg PET, SUV max do 3,8 [Im fuz 86]. Węzły chłonne grupy V po stronie lewej średnicy do 19mm, SUV max 3,0 Węzły chłonne grupy V po stronie prawej średnicy do 17mm, SUV max 4,0 Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Masa resztkowa w śródpiersiu przednim po stronie lewej wielkości ok 23x64mm [Im fuz 112] oraz po stronie prawej 65x29mm [Im fuz 110] , w jej obrębie widoczne są obszary zwiększonego metabolizmu FDG średnicy wg PET do 14mm, SUV max do 6,4. Aktywne metabolicznie węzły chłonne śródpiersiowe, największe: - podostrogowe 44x19mm [SUV max 3,0 [I,m fuz 121] - przytchawicze górne prawe wielkości do 20x24mm [Im fuz 102] SUV max do 4,0, lewe 21x18mm SUV max 3,2 [Im fuz 105] Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej klatki piersiowej, SUV max do 21,0, w jej obrębie widoczne są drobne węzły chłonne. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Nieznacznie zwiększona ilość płynu w osierdziu.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masa miękkotkankowa we wnęce śledziony średnicy ok 22mm.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono obecność aktywnych metabolicznie obszarów w obrębie masy resztkowej w śródpiersiu przednim, węzłach przytchawiczych i podostrogowych oraz szyjnych po stronie lewej. W porównaniu do badania wyjściowego z 29.03.2021 znaczna regresja metaboliczna i radiologiczna zmian.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>24</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 57min od podania 18F-FDG. Glikemia: 90mg%.</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej, SUV max do 7,4, w jej obrębie widoczne są pojedyncze bardzo drobne węzły chłonne. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne grupy IV po stronie lewej średnicy 20m [Im TK 244]. Węzły chłonne grupy V po stronie lewej średnicy do 11mm.  Klatka piersiowa i śródpiersie: Masa resztkowa w śródpiersiu przednim po stronie lewej wielkości ok 22x14mm [Im TK 286] oraz po stronie prawej średnicy 25x12mm [Im TK 304]. Węzły chłonne śródpiersiowe przytchawicze prawe średnicy do 9mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masa miękkotkankowa we wnęce śledziony średnicy ok 10mm [lm TK 443].  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.  Inne: Rozlana aktywność metaboliczna w mięśniach kończyny górnej prawej oraz obręczy barkowej po stronie prawej, mięśni lędźwiowych - w pierwszej kolejności zmiany przeciążeniowe. Aktywność metaboliczna w brunatnej tkance tłuszczowej karku, klatki piersiowej i jamy brzusznej.  Wartości referencyjne: MBPS SUVmax  2,0, Prawy płat wątroby SUVmax do 2,5.</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Aktywność metaboliczna w topografii brunatnej tkanki tłuszczowej, SUV max do 7,4, w jej obrębie widoczne są pojedyncze bardzo drobne węzły chłonne. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Węzły chłonne grupy IV po stronie lewej średnicy 20m [Im TK 244]. Węzły chłonne grupy V po stronie lewej średnicy do 11mm.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Masa resztkowa w śródpiersiu przednim po stronie lewej wielkości ok 22x14mm [Im TK 286] oraz po stronie prawej średnicy 25x12mm [Im TK 304]. Węzły chłonne śródpiersiowe przytchawicze prawe średnicy do 9mm. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masa miękkotkankowa we wnęce śledziony średnicy ok 10mm [lm TK 443].</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym. Dyskopatia L5/S1.  Inne: Rozlana aktywność metaboliczna w mięśniach kończyny górnej prawej oraz obręczy barkowej po stronie prawej, mięśni lędźwiowych - w pierwszej kolejności zmiany przeciążeniowe. Aktywność metaboliczna w brunatnej tkance tłuszczowej karku, klatki piersiowej i jamy brzusznej.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono cech aktywnej metabolicznie choroby chłoniakowej.  Masy resztkowe do kontroli.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>7.4</v>
       </c>
     </row>
